--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_1.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_1.xlsx
@@ -471,11 +471,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>48181</v>
+        <v>29445</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Murilo Oliveira</t>
+          <t>Diogo Barros</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -485,234 +485,234 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45088</v>
+        <v>45098</v>
       </c>
       <c r="G2" t="n">
-        <v>9200.51</v>
+        <v>5958.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>70413</v>
+        <v>96732</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sarah da Mota</t>
+          <t>Anthony Pereira</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45078</v>
+        <v>45097</v>
       </c>
       <c r="G3" t="n">
-        <v>4906.27</v>
+        <v>9801.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>43096</v>
+        <v>84475</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>André Fogaça</t>
+          <t>Sofia Silveira</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45087</v>
+        <v>45094</v>
       </c>
       <c r="G4" t="n">
-        <v>8288.440000000001</v>
+        <v>10993.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3653</v>
+        <v>43777</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ana Lívia Dias</t>
+          <t>Marcos Vinicius Ribeiro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45102</v>
+        <v>45104</v>
       </c>
       <c r="G5" t="n">
-        <v>8895.469999999999</v>
+        <v>6429.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>27227</v>
+        <v>943</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bruna Nascimento</t>
+          <t>Thales Martins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45079</v>
+        <v>45098</v>
       </c>
       <c r="G6" t="n">
-        <v>2858.99</v>
+        <v>7776.68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>38773</v>
+        <v>44083</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sr. Pietro da Cunha</t>
+          <t>Lucca Correia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45104</v>
+        <v>45083</v>
       </c>
       <c r="G7" t="n">
-        <v>4180.8</v>
+        <v>11572.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>86651</v>
+        <v>60057</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Laís Lopes</t>
+          <t>Luigi Teixeira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45094</v>
+        <v>45104</v>
       </c>
       <c r="G8" t="n">
-        <v>12405.18</v>
+        <v>9765.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>21760</v>
+        <v>92572</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Maria Vitória Rezende</t>
+          <t>Lucas Ribeiro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>7</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45100</v>
+        <v>45085</v>
       </c>
       <c r="G9" t="n">
-        <v>5800.12</v>
+        <v>5363.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2383</v>
+        <v>72304</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nathan Castro</t>
+          <t>Maria Julia da Conceição</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,42 +721,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45100</v>
+        <v>45097</v>
       </c>
       <c r="G10" t="n">
-        <v>10196.16</v>
+        <v>9631.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>49984</v>
+        <v>67797</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Luiza Martins</t>
+          <t>Leonardo Souza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45093</v>
+        <v>45086</v>
       </c>
       <c r="G11" t="n">
-        <v>6505.24</v>
+        <v>11206.61</v>
       </c>
     </row>
   </sheetData>
